--- a/trunk/plan/excel/BUFF表.xlsx
+++ b/trunk/plan/excel/BUFF表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25185" windowHeight="7995"/>
+    <workbookView windowWidth="27465" windowHeight="8655"/>
   </bookViews>
   <sheets>
     <sheet name="BuffCFG" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-施加效果时生效</t>
+是否是DOT（0为瞬发，1为持续）</t>
         </r>
       </text>
     </comment>
@@ -72,7 +72,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-周期魔法效果</t>
+是否是Debuff效果</t>
         </r>
       </text>
     </comment>
@@ -94,7 +94,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-持续回合数</t>
+施加效果时生效</t>
         </r>
       </text>
     </comment>
@@ -116,7 +116,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-结束效果时生效</t>
+周期魔法效果</t>
         </r>
       </text>
     </comment>
@@ -138,7 +138,51 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-BUFF类型，相同BUFF类型默认覆盖</t>
+持续回合数，每个回合结束后进行一次效果触发</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+结束效果时生效（用于处理二段伤害等特殊效果）</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+BUFF类型，相同BUFF类型默认覆盖，0为可叠加BUFF</t>
         </r>
       </text>
     </comment>
@@ -147,7 +191,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="27">
   <si>
     <t>ID</t>
   </si>
@@ -158,24 +202,27 @@
     <t>Desc</t>
   </si>
   <si>
-    <t>StartEff</t>
-  </si>
-  <si>
-    <t>CycleEff</t>
+    <t>IsDot</t>
+  </si>
+  <si>
+    <t>IsDebuff</t>
+  </si>
+  <si>
+    <t>StartEffs</t>
+  </si>
+  <si>
+    <t>CycleEffs</t>
   </si>
   <si>
     <t>Duration</t>
   </si>
   <si>
-    <t>EndEff</t>
+    <t>EndEffs</t>
   </si>
   <si>
     <t>BuffType</t>
   </si>
   <si>
-    <t>EffectIds</t>
-  </si>
-  <si>
     <t>Level</t>
   </si>
   <si>
@@ -191,7 +238,7 @@
     <t>number</t>
   </si>
   <si>
-    <t>int[]</t>
+    <t>number[]</t>
   </si>
   <si>
     <t>炎爆</t>
@@ -200,22 +247,31 @@
     <t>瞬间造成伤害</t>
   </si>
   <si>
+    <t>skill_fireball</t>
+  </si>
+  <si>
     <t>灼烧</t>
   </si>
   <si>
     <t>持续收到火焰伤害</t>
   </si>
   <si>
-    <t>1,2</t>
-  </si>
-  <si>
-    <t>skill_fireball</t>
-  </si>
-  <si>
     <t>治疗</t>
   </si>
   <si>
+    <t>造成一次瞬间治疗</t>
+  </si>
+  <si>
     <t>愈合</t>
+  </si>
+  <si>
+    <t>进行持续治疗效果</t>
+  </si>
+  <si>
+    <t>狂暴</t>
+  </si>
+  <si>
+    <t>提升攻击力，减少护甲值</t>
   </si>
 </sst>
 </file>
@@ -840,8 +896,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1188,14 +1245,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
-    <col min="3" max="8" width="17.125" customWidth="1"/>
-    <col min="9" max="9" width="10.375" customWidth="1"/>
+    <col min="3" max="3" width="23.375" customWidth="1"/>
+    <col min="4" max="10" width="17.125" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1229,103 +1287,236 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" t="s">
         <v>14</v>
-      </c>
-      <c r="J2" t="s">
-        <v>11</v>
       </c>
       <c r="K2" t="s">
         <v>12</v>
       </c>
+      <c r="L2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:12">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>101</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:12">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>102</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4" t="s">
         <v>18</v>
       </c>
-      <c r="D4"/>
-      <c r="I4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4" t="s">
-        <v>20</v>
-      </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:12">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
       </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>201</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:12">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>202</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:12">
       <c r="A7">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9">
-        <v>7</v>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
+        <v>301303</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
+        <v>302304</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/trunk/plan/excel/BUFF表.xlsx
+++ b/trunk/plan/excel/BUFF表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27465" windowHeight="8655"/>
+    <workbookView windowWidth="30585" windowHeight="8985"/>
   </bookViews>
   <sheets>
     <sheet name="BuffCFG" sheetId="1" r:id="rId1"/>

--- a/trunk/plan/excel/BUFF表.xlsx
+++ b/trunk/plan/excel/BUFF表.xlsx
@@ -1348,15 +1348,11 @@
       <c r="F3">
         <v>101</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
+      <c r="G3"/>
       <c r="H3">
         <v>0</v>
       </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
+      <c r="I3"/>
       <c r="J3">
         <v>0</v>
       </c>
@@ -1383,18 +1379,14 @@
       <c r="E4">
         <v>0</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
+      <c r="F4"/>
       <c r="G4">
         <v>102</v>
       </c>
       <c r="H4">
         <v>3</v>
       </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
+      <c r="I4"/>
       <c r="J4">
         <v>0</v>
       </c>
@@ -1424,15 +1416,11 @@
       <c r="F5">
         <v>201</v>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
+      <c r="G5"/>
       <c r="H5">
         <v>0</v>
       </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
+      <c r="I5"/>
       <c r="J5">
         <v>0</v>
       </c>
@@ -1459,18 +1447,14 @@
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
+      <c r="F6"/>
       <c r="G6">
         <v>202</v>
       </c>
       <c r="H6">
         <v>3</v>
       </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
+      <c r="I6"/>
       <c r="J6">
         <v>0</v>
       </c>
@@ -1500,9 +1484,7 @@
       <c r="F7" s="1">
         <v>301303</v>
       </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
+      <c r="G7"/>
       <c r="H7">
         <v>0</v>
       </c>

--- a/trunk/plan/excel/BUFF表.xlsx
+++ b/trunk/plan/excel/BUFF表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30585" windowHeight="8985"/>
+    <workbookView windowWidth="22350" windowHeight="11055"/>
   </bookViews>
   <sheets>
     <sheet name="BuffCFG" sheetId="1" r:id="rId1"/>
@@ -437,12 +437,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1348,11 +1348,9 @@
       <c r="F3">
         <v>101</v>
       </c>
-      <c r="G3"/>
       <c r="H3">
         <v>0</v>
       </c>
-      <c r="I3"/>
       <c r="J3">
         <v>0</v>
       </c>
@@ -1377,16 +1375,14 @@
         <v>1</v>
       </c>
       <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4"/>
+        <v>1</v>
+      </c>
       <c r="G4">
         <v>102</v>
       </c>
       <c r="H4">
         <v>3</v>
       </c>
-      <c r="I4"/>
       <c r="J4">
         <v>0</v>
       </c>
@@ -1416,11 +1412,9 @@
       <c r="F5">
         <v>201</v>
       </c>
-      <c r="G5"/>
       <c r="H5">
         <v>0</v>
       </c>
-      <c r="I5"/>
       <c r="J5">
         <v>0</v>
       </c>
@@ -1447,14 +1441,12 @@
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6"/>
       <c r="G6">
         <v>202</v>
       </c>
       <c r="H6">
         <v>3</v>
       </c>
-      <c r="I6"/>
       <c r="J6">
         <v>0</v>
       </c>
@@ -1484,7 +1476,6 @@
       <c r="F7" s="1">
         <v>301303</v>
       </c>
-      <c r="G7"/>
       <c r="H7">
         <v>0</v>
       </c>

--- a/trunk/plan/excel/BUFF表.xlsx
+++ b/trunk/plan/excel/BUFF表.xlsx
@@ -437,12 +437,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/trunk/plan/excel/BUFF表.xlsx
+++ b/trunk/plan/excel/BUFF表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22350" windowHeight="11055"/>
+    <workbookView windowWidth="27030" windowHeight="12825"/>
   </bookViews>
   <sheets>
     <sheet name="BuffCFG" sheetId="1" r:id="rId1"/>
@@ -1477,7 +1477,7 @@
         <v>301303</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I7" s="1">
         <v>302304</v>

--- a/trunk/plan/excel/BUFF表.xlsx
+++ b/trunk/plan/excel/BUFF表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27030" windowHeight="12825"/>
+    <workbookView windowWidth="24570" windowHeight="10290"/>
   </bookViews>
   <sheets>
     <sheet name="BuffCFG" sheetId="1" r:id="rId1"/>
@@ -191,7 +191,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="29">
   <si>
     <t>ID</t>
   </si>
@@ -272,6 +272,12 @@
   </si>
   <si>
     <t>提升攻击力，减少护甲值</t>
+  </si>
+  <si>
+    <t>眩晕</t>
+  </si>
+  <si>
+    <t>造成眩晕</t>
   </si>
 </sst>
 </file>
@@ -1245,8 +1251,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col min="3" max="3" width="23.375" customWidth="1"/>
     <col min="4" max="10" width="17.125" customWidth="1"/>
@@ -1492,6 +1498,38 @@
         <v>18</v>
       </c>
     </row>
+    <row r="8" spans="1:12">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>501</v>
+      </c>
+      <c r="H8">
+        <v>2</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8" t="s">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
